--- a/backend/data/financials_by_company/0146.HK.xlsx
+++ b/backend/data/financials_by_company/0146.HK.xlsx
@@ -3738,182 +3738,182 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -4060,7 +4060,7 @@
         <v>3.87</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.228</v>
+        <v>0.213</v>
       </c>
       <c r="AI2" t="n">
         <v>7.7999997</v>
@@ -4072,7 +4072,7 @@
         <v>3000</v>
       </c>
       <c r="AL2" t="n">
-        <v>11915</v>
+        <v>9620</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -4081,10 +4081,10 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4114,10 +4114,10 @@
         <v>0.50158423</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.5714</v>
+        <v>1.5564</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.7529</v>
+        <v>1.75135</v>
       </c>
       <c r="BB2" t="n">
         <v>0.12</v>
@@ -4188,10 +4188,10 @@
         <v>2.811</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.09859156600000001</v>
+        <v>0.08333337</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.12</v>
@@ -4307,135 +4307,135 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="n">
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>1780455665</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>finmb_877162</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1739967022</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1739967022</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.0036000013</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.0023130311</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.1913501</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.10925863</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>947035800000</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.099999905</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>1.56 - 1.56</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>9620</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.13999999</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.098591544</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>1.42 - 2.0</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.44000006</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.22000003</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>8.333337999999999</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>TAI PING CARPET</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
         <v>6.8493085</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="EO2" t="n">
         <v>1.56</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>TAI PING CARPET</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.099999905</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>1.56 - 1.56</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>11915</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.13999999</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.098591544</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>1.42 - 2.0</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.44000006</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.22000003</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>9.859157</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1739967022</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1739967022</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.011400104</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.007254743</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.19290006</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.110046245</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>947035800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>1780455665</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>finmb_877162</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
